--- a/iwpb-sg-dashboard/sample/IWPB_unit_and_rollup_sample.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_unit_and_rollup_sample.xlsx
@@ -450,7 +450,7 @@
     <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="46.83203125" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="17.83203125" customWidth="1"/>
     <col min="7" max="7" width="11.83203125" customWidth="1"/>
@@ -773,7 +773,7 @@
         <v>number</v>
       </c>
       <c r="E15" s="2" t="str">
-        <v>m</v>
+        <v>mn</v>
       </c>
       <c r="F15" s="5">
         <v>162369</v>
@@ -973,7 +973,7 @@
         <v>no total</v>
       </c>
       <c r="D26" s="2" t="str">
-        <v>%, number, m, US$m are never added together</v>
+        <v>%, number, mn, US$m are never added together</v>
       </c>
     </row>
     <row r="28">
